--- a/Lista de Objetos.xlsx
+++ b/Lista de Objetos.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sala 1 EEST 1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEFF5E9A-7C1A-4DC6-B2CF-850219E69593}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9675" xr2:uid="{40C98CBD-7B94-42DE-ABA0-0A943CD2B391}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4575"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Actividades</t>
   </si>
@@ -45,17 +44,20 @@
     <t>Practicar C++ para el prototipo</t>
   </si>
   <si>
-    <t>Realizar Subtareas del prototipo</t>
-  </si>
-  <si>
     <t>Finalizar el prototipo</t>
+  </si>
+  <si>
+    <t>Realizar un control de producto</t>
+  </si>
+  <si>
+    <t>Realizar el prototipo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,8 +65,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -89,8 +98,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -98,16 +113,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="17" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,8 +469,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D5B1CA0-00A4-4878-975C-7E382D220F21}">
-  <dimension ref="A1:I8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
@@ -482,28 +530,38 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="1"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="F6" s="6"/>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G7" s="5"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>